--- a/reports/shell_script/report.xlsx
+++ b/reports/shell_script/report.xlsx
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc59-7664-76b0-b6ff-10345890c21e</t>
+    <t>01a0cce2-c5fd-78d0-921d-07549798c762</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc59-766d-7760-a5b3-d40c966889aa</t>
+    <t>01a0cce2-c607-7773-85f0-ba9b232ed984</t>
   </si>
   <si>
     <t>Fresh input</t>
@@ -350,8 +350,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_042281872ec49cf6006ab34a1b3f0c87d2b4664d7e21a3d97f", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0obmfE5rLHoPc2Q8CA1pWSImS8yT-lr2CHuzzW2Kaq1AJCQPxiA5xzZHltiBqBPWTHvGDyNzzTS8Pd1NxL8RKdKLbgoUCtuXTfpBHELtcFShfc4k_CC-YrrSN9dOQXhijQqSJmy8mrxYHJjoosIyT3LVIZG9LtcvfSTBIH_CKcKpAWzUBBgPnSb1d3poEa8mzVYQajJpPO3JnX8QWW3cFqnui03M4FOMwgbKFX1bUXN4MVrTVdgVLbTQrtqqtDex-MoiIhJNOrneWiTVNkSwtZV44ZjrAp17h3ryRG-DrLo8pZW_vl5euImjdftixG0Fb_ttl4kCDrolUdgEO0KjgWFsXbhwRfBRJXzg1fKeMndI4df0_72M3LK2Yci0zLjN7eSHYUMkgTpEVlaFC1WSMc-RLogQ7UJTbjV720hAbZGmPKBMEueICRK1T3cixyi-_1LiqawwxmI-hKuie1-MwTxlTzgteZBoeFyo0_L2EvPBTmtx6EzQKfHHpH8g9boZOuUXVItUzdDcwAvXLeP2BNX1Nk00-5x2HS_o_mAW6L-1YeV7ulQmYTz8owBAWXMLoEOQ0QXzl13AGBnFIpPCuptWIsrivkJ8Aw-47OyfO7kT9pOKHWCHbMeEVH9xk33GH0iZWie5QQy_a1td2MwHnG_qAThAIXzbFkD7ybib0V9O4GN5olyoS6iClLz7MfH6A27qih3aW3GLsLInBKaVj0D0LX2Ky2t29PFk25zHiLoabHNOOELrUx8lLMuRw8lw5x-XG6o7qhI8iPIqKTWAv_JBnO5OQBZuXXAsosJyOsmXrgZ--AxPkH6rGJYQfP6Uk00EaVbo7K239x62XWIW-jAg9MqoPRL9cKBvbwZ-01G3zPvq6bnJfVLpNjlpAUbD4vH8wO6zuNEtB9RJYEgc9EHexqePbNlwbtmnd7CTeFqEJ8zZrHEOF44uIo3g4aHc2i7zYXDOPpbH9lQKhfkIOg3w_JNr1fFc9qowHr8-NESCKuSUE8m6XyVez0xiG_WzMVbkmoNcePb3Vw7ZvR0pEjWnQ8o5GPOArM3v3niNrhR4-tCijfmf3OU0A4LRqm2bSQRHFFDkmaBss95NBLJd4BcIJx0_E3t-k6Bw5dEYFrrxwH-Ode2fqPq8kj0U2nFo0bno4cyGbOB51dCqZTB5AAN9-ica5IrRtECGdGsX7n116eDcTQProirtsKdYmxGAkdd"}, {"type": "function_call", "name": "execute", "arguments": "{\"command\":\"sh ./summarize.sh\",\"timeout\":120}", "call_id": "call_AYk1RqU3vaNO6osRnAExUeK8", "id": "fc_042281872ec49cf6006ab34a1b6ba087d2a53aadf185bcf139", "index": 1}]
-{"name": "execute", "args": {"command": "sh ./summarize.sh", "timeout": 120}, "id": "call_AYk1RqU3vaNO6osRnAExUeK8", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0967585e220fda42006ab36d430e3c87d2b7c939b8f5a054dd", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21DI4VJMv699J-YjN9sGPspsQp6Ve4s3Xd3eVoIUShuESZPf9MU7W-bdMhcn-9dKyNzvh2d24tDr0rxfueVqcqGwQGYBFQOwvPmaYQtpZIuxujrIbNTXbNRTz96DiWFgNiV9OBlZUpRYUBbtK2VsqNms2qTT8XT10kgVpoCT7XOd7mXCwvHJaVzTwc5KlMyAPAdOnhsxu7j15nZgZpXDEF8zoOL-YGPZ6jAnyrlxexRGCuIUc7LZmntoBiFCwrq7XussfMZpp-kdBSDUWCGZif1q8A15tvPRpC6LOxdXdLjX1VHGTjR_BBStDMhI4tOvhQMZ6nt6Hw61rbJwo8ZDaQO_T4oVUiwjofM9qaWNiKsLKxMHspRcTgWcFIajmuFLTK8AqDXmT6tLNjOUgUBAyzQOKkX39fkRE0G5wMGpKTbM9bq_pH_PJLdjZIYdtai5mawnuu2ytyNFtd2F7uYqW66WFsJ2VvYjaNuW8mSe7LriUjiHsTMIBXIhjkLaqJVEGKYE8AfUT7clf8xsKVXMS1qfLcFeDiCWpIB08WjgDybtgoMXtJTLLIAKfk4Seqs_vl_LZ3PkP8kiHLI3RF6cs6TZMU0DO9cxf9bZVE3Y4kAEfMpuWULdNh66lPMeQJr94g-_Nwl2zVqZWyzVcxBQzPyidt_IFvjgGZDQcEQ_3bQ80ppwJHOIRR8gLVqRwjcX2SCNeKWh1gW_VD1ZicbTC3FC-hJ9NbceLh8eOHyjRtuRaOr6z54HHnJ3iTMguoX3qM4DJYHPh_1ydi6Agwd3e5OTZ_EKLt1stpCioZ8hnZUvC9NVccTW3HI57HZthMUaDAbxUo2W0Nl5bY_UEkzIx9zj5sOM1bLhrBcxx4kibBhLamepDyM5yN9bJCXPIfFuOtY7Jv9bVYpw5XexfP1D2gm7EDsYVHGfu6poEYnTe6n4uNkaPazFL3QMpHKyyppcthCD2l-AVtkPkjfMV4uVKmC-ypPfkLsyOLFRx035LFLQtoFcMr6M51zbAmecpEjaYnzE8bm_jyx0DkUU-mnpSZpvzcRN5nmIZFAeTlt7zMc6XZEte-VgqB-QBQfFS1iK-qiEIwdZjqD_80vY_e0DrgEA7-yRO3MNqRD4psYeDA_9Oi-KVA79OKLpPEpGIzhIHovTExVJ-1gN912qkHpPXfdQRCDb2VELcleXzykM35mm6gV38sC-SjscpJ2QF866TyT"}, {"type": "function_call", "name": "execute", "arguments": "{\"command\":\"sh ./summarize.sh\",\"timeout\":120}", "call_id": "call_Q66W87QSm7grtEa7O5oUdksk", "id": "fc_0967585e220fda42006ab36d434a2087d2b56f51d294a32f8e", "index": 1}]
+{"name": "execute", "args": {"command": "sh ./summarize.sh", "timeout": 120}, "id": "call_Q66W87QSm7grtEa7O5oUdksk", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -363,7 +363,7 @@
     <t>Tool · execute</t>
   </si>
   <si>
-    <t>01a0cc59-7c4a-7461-9e7a-d40e79735ec8</t>
+    <t>01a0cce2-d033-78c2-b1a4-dc06cd1ac6bc</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -383,7 +383,7 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cc59-7c7e-7ae0-9682-39c0c81cdbd7</t>
+    <t>01a0cce2-d060-7183-be50-f3539cfcd9b5</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "Orders: 3  \nTotal units: 9  \n\nExit status: 0", "phase": "final_answer", "index": 0, "id": "msg_042281872ec49cf6006ab34a1c59bc87d2a5c6fa45392c3195"}]</t>
+    <t>[{"type": "text", "text": "Order totals:\n- Orders: 3\n- Total units: 9\n\nExit status: 0", "phase": "final_answer", "index": 0, "id": "msg_0967585e220fda42006ab36d445d4487d2b0db9897a9c06878"}]</t>
   </si>
   <si>
     <t>shell_agent</t>
@@ -413,7 +413,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cc59-7667-7301-b029-dd4181ed2865</t>
+    <t>01a0cce2-c600-70b3-bba3-a4088cc2c75c</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -425,7 +425,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cc59-7668-7361-accd-ddaa45c0c98c</t>
+    <t>01a0cce2-c601-77d3-9bac-2a73cea15bc7</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -446,7 +446,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cc59-7c48-79a3-802c-8fd967d70237</t>
+    <t>01a0cce2-d032-76c2-8f9f-25c9264a81ae</t>
   </si>
   <si>
     <t xml:space="preserve">        execute</t>
@@ -466,7 +466,7 @@
 Only available on backends implementing SandboxBackendProtocol; otherwise it returns an error.</t>
   </si>
   <si>
-    <t>01a0cc59-7c7c-7ec3-8722-973bba848f13</t>
+    <t>01a0cce2-d05e-7ea2-9e8f-10fa6f7a360c</t>
   </si>
 </sst>
 </file>
@@ -934,11 +934,11 @@
       </c>
       <c r="E2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006187196988</v>
+        <v>0.0006239539188</v>
       </c>
       <c r="F2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00070924</v>
+        <v>0.00071524</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
@@ -946,7 +946,7 @@
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -958,11 +958,11 @@
       </c>
       <c r="E3" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006187196988</v>
+        <v>0.0006239539188</v>
       </c>
       <c r="F3" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00070924</v>
+        <v>0.00071524</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -970,7 +970,7 @@
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1425,7 +1425,7 @@
         <v>105</v>
       </c>
       <c r="D27" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
@@ -1439,23 +1439,23 @@
         <v>107</v>
       </c>
       <c r="D28" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.093688e-05</v>
+        <v>2.61711e-05</v>
       </c>
       <c r="F28" s="2">
         <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.4e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="G28" s="5">
         <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H28" s="5">
         <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="47" customHeight="1">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="E32" s="2">
         <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28)=4,SUM('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28),"Unknown")</f>
-        <v>7.63236513e-05</v>
+        <v>8.15578713e-05</v>
       </c>
       <c r="F32" s="2">
         <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28)=4,SUM('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28),"Unknown")</f>
-        <v>8.749e-05</v>
+        <v>9.349e-05</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1704,15 +1704,15 @@
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D13,'Turns'!D28)=2,SUM('Turns'!D13,'Turns'!D28),"Unknown")</f>
-        <v>48.0</v>
+        <v>53.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
-        <v>5.0248512e-05</v>
+        <v>5.5482732e-05</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
-        <v>5.76e-05</v>
+        <v>6.36e-05</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
@@ -1728,11 +1728,11 @@
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006187196988</v>
+        <v>0.0006239539188</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00070924</v>
+        <v>0.00071524</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1740,10 +1740,10 @@
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2463.695</v>
+        <v>4456.8</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>126</v>
@@ -1775,7 +1775,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.408</v>
+        <v>0.426</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>130</v>
@@ -1880,7 +1880,7 @@
         <v>62.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>1502.607</v>
+        <v>2607.991</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>126</v>
@@ -1991,7 +1991,7 @@
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>1494.555</v>
+        <v>2601.198</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>137</v>
@@ -2023,7 +2023,7 @@
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>50.148</v>
+        <v>42.343</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>130</v>
@@ -2055,7 +2055,7 @@
         <v>140</v>
       </c>
       <c r="AD7" s="1">
-        <v>46.919</v>
+        <v>40.041</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>130</v>
@@ -2124,15 +2124,15 @@
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.093688e-05</v>
+        <v>2.61711e-05</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>2.4e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
@@ -2145,11 +2145,11 @@
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.63236513e-05</v>
+        <v>8.15578713e-05</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>8.749e-05</v>
+        <v>9.349e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2160,7 +2160,7 @@
         <v>9.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>903.275</v>
+        <v>1801.011</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>126</v>
@@ -2232,15 +2232,15 @@
       </c>
       <c r="S9" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="T9" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.093688e-05</v>
+        <v>2.61711e-05</v>
       </c>
       <c r="U9" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>2.4e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="V9" s="2">
         <v>0</v>
@@ -2253,11 +2253,11 @@
       </c>
       <c r="Y9" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.63236513e-05</v>
+        <v>8.15578713e-05</v>
       </c>
       <c r="Z9" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>8.749e-05</v>
+        <v>9.349e-05</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2271,7 +2271,7 @@
         <v>118</v>
       </c>
       <c r="AD9" s="1">
-        <v>899.312</v>
+        <v>1797.868</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>137</v>

--- a/reports/shell_script/report.xlsx
+++ b/reports/shell_script/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="145">
   <si>
     <t>Request</t>
   </si>
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cce2-c5fd-78d0-921d-07549798c762</t>
+    <t>01a0d142-4fb9-74b1-9161-3e9286297f58</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,13 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cce2-c607-7773-85f0-ba9b232ed984</t>
-  </si>
-  <si>
-    <t>Fresh input</t>
+    <t>01a0d142-4fc4-7743-8b54-9fbce1d8ddab</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -350,8 +353,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0967585e220fda42006ab36d430e3c87d2b7c939b8f5a054dd", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21DI4VJMv699J-YjN9sGPspsQp6Ve4s3Xd3eVoIUShuESZPf9MU7W-bdMhcn-9dKyNzvh2d24tDr0rxfueVqcqGwQGYBFQOwvPmaYQtpZIuxujrIbNTXbNRTz96DiWFgNiV9OBlZUpRYUBbtK2VsqNms2qTT8XT10kgVpoCT7XOd7mXCwvHJaVzTwc5KlMyAPAdOnhsxu7j15nZgZpXDEF8zoOL-YGPZ6jAnyrlxexRGCuIUc7LZmntoBiFCwrq7XussfMZpp-kdBSDUWCGZif1q8A15tvPRpC6LOxdXdLjX1VHGTjR_BBStDMhI4tOvhQMZ6nt6Hw61rbJwo8ZDaQO_T4oVUiwjofM9qaWNiKsLKxMHspRcTgWcFIajmuFLTK8AqDXmT6tLNjOUgUBAyzQOKkX39fkRE0G5wMGpKTbM9bq_pH_PJLdjZIYdtai5mawnuu2ytyNFtd2F7uYqW66WFsJ2VvYjaNuW8mSe7LriUjiHsTMIBXIhjkLaqJVEGKYE8AfUT7clf8xsKVXMS1qfLcFeDiCWpIB08WjgDybtgoMXtJTLLIAKfk4Seqs_vl_LZ3PkP8kiHLI3RF6cs6TZMU0DO9cxf9bZVE3Y4kAEfMpuWULdNh66lPMeQJr94g-_Nwl2zVqZWyzVcxBQzPyidt_IFvjgGZDQcEQ_3bQ80ppwJHOIRR8gLVqRwjcX2SCNeKWh1gW_VD1ZicbTC3FC-hJ9NbceLh8eOHyjRtuRaOr6z54HHnJ3iTMguoX3qM4DJYHPh_1ydi6Agwd3e5OTZ_EKLt1stpCioZ8hnZUvC9NVccTW3HI57HZthMUaDAbxUo2W0Nl5bY_UEkzIx9zj5sOM1bLhrBcxx4kibBhLamepDyM5yN9bJCXPIfFuOtY7Jv9bVYpw5XexfP1D2gm7EDsYVHGfu6poEYnTe6n4uNkaPazFL3QMpHKyyppcthCD2l-AVtkPkjfMV4uVKmC-ypPfkLsyOLFRx035LFLQtoFcMr6M51zbAmecpEjaYnzE8bm_jyx0DkUU-mnpSZpvzcRN5nmIZFAeTlt7zMc6XZEte-VgqB-QBQfFS1iK-qiEIwdZjqD_80vY_e0DrgEA7-yRO3MNqRD4psYeDA_9Oi-KVA79OKLpPEpGIzhIHovTExVJ-1gN912qkHpPXfdQRCDb2VELcleXzykM35mm6gV38sC-SjscpJ2QF866TyT"}, {"type": "function_call", "name": "execute", "arguments": "{\"command\":\"sh ./summarize.sh\",\"timeout\":120}", "call_id": "call_Q66W87QSm7grtEa7O5oUdksk", "id": "fc_0967585e220fda42006ab36d434a2087d2b56f51d294a32f8e", "index": 1}]
-{"name": "execute", "args": {"command": "sh ./summarize.sh", "timeout": 120}, "id": "call_Q66W87QSm7grtEa7O5oUdksk", "type": "tool_call"}</t>
+    <t>[{"id": "rs_056f2f78f65d105c006ab48bdc549c87d2ba63244a0418f912", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIvca-dztntiyaCCQTmPZ7cet6acr5BMOlGTEjxa1kMiyCRnLbg_hLHVSizBsjibwMS05hjhM9yIRJsdJWwYjgUgxAs_pG5zSX6XyKUJuUD5Hl3NecqcHtnLCvISyzM0oc28MZNP0C9YMFG9WAsIDdJBIeNBWojWm_yueEKhFQKFFfjRneUea_IRcnF-GbYm4Z5YX1xKX_wicLYUZ_54iItcAzog3JWM1U8zSOfabQS-AeJOE2CxRiwQy9PccIzIv5tdd74YNSwtvOJY9QwqZVaVL7esJM0x7k5HTjM9o2WtCviAfZtp0U-8i_p4xhztFE4gwE_x6oOKvkiHOZI-WwT66d_An53eXb-lHYl5pdewp3vRn1lEPeE9gtwzhHh6Mf0ckbczy1EaaTk4QWmtr7dk1xHr8aVDh7o_2xjLOunauEW9RyopaLiKR1R_hXYHJUUSAMnMW5to55nd7ESQX11fOBgO31JvoxVXLJy1lW829OdzQ4MPPQjOpzJHezSvgNnBNfcWtMn2v-Iu0d1QWfbreq9gTvYSIabbtQIcFxUaae-sDWBnRUvVKsIFknV85srM9CBP1tEQBIfCQCe0wjP0IJ0lrAI8272gkGt0hjzByHpq6Q9Lld0CLTIKYgeWHl4d9SdgSHSRVPblTfzGSsMfcQaJq41vNMyhY5NOFZVW-BdpHnuhvpEsu3ZsEOfmg8Yg2NZl7iL9qmzAyONwozFhvRWArKfpscEAmmznxhhJmeMFVkcBThyVMALAtSl-nJGWW8mgx5I2d2Wla3WdYJMOlKoDC9iQucjiLouvrAEnezPXBiIhqJSkcxbs7Kgg8bfb170cwqbT7YnOS76nRR2RwH2kkeCJYhrgK_9YLncVIAKFLUNg1RGCeGd4KggzrsOSON9qbmbNzRRfOdmEqcTMo2KKigtjvOpGMmA1IadP4n1b-ogstLuS76OPuQH6HBNOVpMj-BRIz3VkmZocFxqMsbWp05cC_Ym6d0hFHm7ofgeGRegPlsROmag3N42YE8i_t414WkcWcQpAoPqFw3O73Yt1Eq_1HbZodCBwJEDueoGpk3U_md6gIWGxFyd7PHnHgrWn8wVIMAaVMJcvLplmY6emxH7Tx-S30kJUTFJtEmLObLgTc86DJ6TXQPKu-WKWq_80rmpexw46AHRnIUJhhHIpm4TLH2pXb94I1F_fyUzAduVyupGX82wJ-sxHEtIt"}, {"type": "function_call", "name": "execute", "arguments": "{\"command\":\"sh ./summarize.sh\",\"timeout\":120}", "call_id": "call_PlpK37RsthN7RecjgOhp11pw", "id": "fc_056f2f78f65d105c006ab48bdc717087d29ed744442d3d816a", "index": 1}]
+{"name": "execute", "args": {"command": "sh ./summarize.sh", "timeout": 120}, "id": "call_PlpK37RsthN7RecjgOhp11pw", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -363,7 +366,7 @@
     <t>Tool · execute</t>
   </si>
   <si>
-    <t>01a0cce2-d033-78c2-b1a4-dc06cd1ac6bc</t>
+    <t>01a0d142-5671-7cd2-b611-d236227197e9</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -383,16 +386,13 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cce2-d060-7183-be50-f3539cfcd9b5</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
+    <t>01a0d142-56a2-7893-85da-b7289e7433ba</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "Order totals:\n- Orders: 3\n- Total units: 9\n\nExit status: 0", "phase": "final_answer", "index": 0, "id": "msg_0967585e220fda42006ab36d445d4487d2b0db9897a9c06878"}]</t>
+    <t>[{"type": "text", "text": "Orders: 3  \nTotal units: 9  \n\nExit status: 0", "phase": "final_answer", "index": 0, "id": "msg_056f2f78f65d105c006ab48bddd1ec87d2924ce6407aa49bd2"}]</t>
   </si>
   <si>
     <t>shell_agent</t>
@@ -413,7 +413,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cce2-c600-70b3-bba3-a4088cc2c75c</t>
+    <t>01a0d142-4fbd-7501-913f-6095a96d4f11</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -425,7 +425,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cce2-c601-77d3-9bac-2a73cea15bc7</t>
+    <t>01a0d142-4fbe-7f61-9336-1195e0309092</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -446,7 +446,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cce2-d032-76c2-8f9f-25c9264a81ae</t>
+    <t>01a0d142-5670-7ae0-8d3e-e5377d43b493</t>
   </si>
   <si>
     <t xml:space="preserve">        execute</t>
@@ -466,7 +466,7 @@
 Only available on backends implementing SandboxBackendProtocol; otherwise it returns an error.</t>
   </si>
   <si>
-    <t>01a0cce2-d05e-7ea2-9e8f-10fa6f7a360c</t>
+    <t>01a0d142-569f-7521-8050-9fa794f475af</t>
   </si>
 </sst>
 </file>
@@ -873,7 +873,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -933,20 +933,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006239539188</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E33)=2,SUM('Turns'!E18,'Turns'!E33),"Unknown")</f>
+        <v>0.000143037847</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00071524</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F33)=2,SUM('Turns'!F18,'Turns'!F33),"Unknown")</f>
+        <v>0.00016322</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>14.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>72.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -957,20 +957,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006239539188</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E33)=2,SUM('Turns'!E18,'Turns'!E33),"Unknown")</f>
+        <v>0.000143037847</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00071524</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F33)=2,SUM('Turns'!F18,'Turns'!F33),"Unknown")</f>
+        <v>0.00016322</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>14.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>72.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1004,23 +1004,23 @@
         <v>97</v>
       </c>
       <c r="D5" s="5">
-        <v>3</v>
+        <v>2307</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>4.0434789e-05</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.614e-05</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
@@ -1033,8 +1033,27 @@
       <c r="C6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="73" customHeight="1">
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G6" s="5">
+        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="5">
+        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="24" customHeight="1">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -1044,11 +1063,8 @@
       <c r="C7" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" customHeight="1">
+    </row>
+    <row r="8" spans="1:13" ht="73" customHeight="1">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -1056,10 +1072,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
@@ -1070,26 +1086,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2307</v>
-      </c>
-      <c r="E9" s="2">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0005031393975</v>
-      </c>
-      <c r="F9" s="2">
-        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00057675</v>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>50.0</v>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
@@ -1103,48 +1103,29 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:13" ht="24" customHeight="1">
+      <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="4">
+    </row>
+    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="4">
         <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24" customHeight="1">
-      <c r="A12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="5">
-        <v>9</v>
-      </c>
-      <c r="E12" s="2">
-        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.421596e-06</v>
-      </c>
-      <c r="F12" s="2">
-        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.08e-05</v>
-      </c>
-      <c r="G12" s="5">
-        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="5">
-        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1158,26 +1139,26 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.36e-05</v>
+        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!F17),D13*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>1.08e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="281" customHeight="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1187,11 +1168,27 @@
       <c r="C14" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="24" customHeight="1">
+      <c r="D14" s="5">
+        <v>28</v>
+      </c>
+      <c r="E14" s="2">
+        <f>IF(AND(ISNUMBER(F14),ISNUMBER('Reference data'!$B$3)),F14*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.944536e-05</v>
+      </c>
+      <c r="F14" s="2">
+        <f>IF(D14=0,0,IF(ISNUMBER('Reference data'!E17),D14*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>3.36e-05</v>
+      </c>
+      <c r="G14" s="5">
+        <f>IF(ISNUMBER(E14),ROUND(E14*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H14" s="5">
+        <f>IF(ISNUMBER(F14),ROUND(F14*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="281" customHeight="1">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -1199,7 +1196,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="24" customHeight="1">
@@ -1213,125 +1213,106 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:13" ht="24" customHeight="1">
+      <c r="A17" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="4">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13)=4,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.0005423960475</v>
-      </c>
-      <c r="F17" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13)=4,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.00062175</v>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>54.0</v>
-      </c>
-      <c r="H17" s="5">
-        <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
-      </c>
-      <c r="K17" s="4" t="s">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="E18" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14)=4,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14),"Unknown")</f>
+        <v>7.9870539e-05</v>
+      </c>
+      <c r="F18" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14)=4,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14),"Unknown")</f>
+        <v>9.114e-05</v>
+      </c>
+      <c r="G18" s="5">
+        <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="H18" s="5">
+        <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M18" s="4" t="s">
+    </row>
+    <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="24" customHeight="1">
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="K19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="I19" s="6" t="s">
+    </row>
+    <row r="20" spans="1:13" ht="24" customHeight="1">
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="60" customHeight="1">
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="I20" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="6" t="s">
+    </row>
+    <row r="21" spans="1:13" ht="60" customHeight="1">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A21" s="4" t="s">
+      <c r="I21" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
+    </row>
+    <row r="22" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="4">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D22" s="4">
         <v>2377</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J22" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="24" customHeight="1">
-      <c r="A22" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="M22" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="D22" s="5">
-        <v>2307</v>
-      </c>
-      <c r="E22" s="2">
-        <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.02511518e-05</v>
-      </c>
-      <c r="F22" s="2">
-        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!C17),D22*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.614e-05</v>
-      </c>
-      <c r="G22" s="5">
-        <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H22" s="5">
-        <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1340,72 +1321,72 @@
         <v>97</v>
       </c>
       <c r="D23" s="5">
-        <v>3</v>
+        <v>2374</v>
       </c>
       <c r="E23" s="2">
         <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>4.1609098e-05</v>
       </c>
       <c r="F23" s="2">
-        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!B17),D23*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!C17),D23*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.748e-05</v>
       </c>
       <c r="G23" s="5">
         <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H23" s="5">
         <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="24" customHeight="1">
+      <c r="A24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="5">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2">
+        <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="F24" s="2">
+        <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!B17),D24*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G24" s="5">
+        <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
         <v>0.0</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="60" customHeight="1">
-      <c r="A24" t="s">
+      <c r="H24" s="5">
+        <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="60" customHeight="1">
+      <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="24" customHeight="1">
-      <c r="A25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="5">
-        <v>67</v>
-      </c>
-      <c r="E25" s="2">
-        <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.46121975e-05</v>
-      </c>
-      <c r="F25" s="2">
-        <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!D17),D25*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>1.675e-05</v>
-      </c>
-      <c r="G25" s="5">
-        <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H25" s="5">
-        <f>IF(ISNUMBER(F25),ROUND(F25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="24" customHeight="1">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1414,53 +1395,34 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="4">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="s">
+    <row r="27" spans="1:13" ht="24" customHeight="1">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="24" customHeight="1">
-      <c r="A28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="5">
-        <v>25</v>
-      </c>
-      <c r="E28" s="2">
-        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.61711e-05</v>
-      </c>
-      <c r="F28" s="2">
-        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3e-05</v>
-      </c>
-      <c r="G28" s="5">
-        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H28" s="5">
-        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="47" customHeight="1">
+    </row>
+    <row r="28" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="4">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="24" customHeight="1">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1468,24 +1430,43 @@
       <c r="C29" t="s">
         <v>108</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="D29" s="5">
+        <v>20</v>
+      </c>
+      <c r="E29" s="2">
+        <f>IF(AND(ISNUMBER(F29),ISNUMBER('Reference data'!$B$3)),F29*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.10324e-05</v>
+      </c>
+      <c r="F29" s="2">
+        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!E17),D29*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.4e-05</v>
+      </c>
+      <c r="G29" s="5">
+        <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H29" s="5">
+        <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="47" customHeight="1">
+      <c r="A30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" s="6" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="24" customHeight="1">
-      <c r="A30" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1494,38 +1475,49 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B32" s="4">
-        <v>1</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="2">
-        <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28)=4,SUM('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28),"Unknown")</f>
-        <v>8.15578713e-05</v>
-      </c>
-      <c r="F32" s="2">
-        <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28)=4,SUM('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28),"Unknown")</f>
-        <v>9.349e-05</v>
-      </c>
-      <c r="G32" s="5">
-        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="H32" s="5">
-        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="K32" s="4" t="s">
+    <row r="32" spans="1:13" ht="24" customHeight="1">
+      <c r="A32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="4">
+        <v>1</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>111</v>
       </c>
+      <c r="E33" s="2">
+        <f>IF(COUNT('Turns'!E23,'Turns'!E24,'Turns'!E29)=3,SUM('Turns'!E23,'Turns'!E24,'Turns'!E29),"Unknown")</f>
+        <v>6.3167308e-05</v>
+      </c>
+      <c r="F33" s="2">
+        <f>IF(COUNT('Turns'!F23,'Turns'!F24,'Turns'!F29)=3,SUM('Turns'!F23,'Turns'!F24,'Turns'!F29),"Unknown")</f>
+        <v>7.208e-05</v>
+      </c>
+      <c r="G33" s="5">
+        <f>IF(ISNUMBER(E33),ROUND(E33*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H33" s="5">
+        <f>IF(ISNUMBER(F33),ROUND(F33*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE32">
+  <conditionalFormatting sqref="A2:AE33">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1658,7 +1650,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>125</v>
@@ -1667,83 +1659,80 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
+        <f>IF(COUNT('Turns'!D6,'Turns'!D24)=2,SUM('Turns'!D6,'Turns'!D24),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="K2" s="2">
+        <f>IF(COUNT('Turns'!E6,'Turns'!E24)=2,SUM('Turns'!E6,'Turns'!E24),"Unknown")</f>
+        <v>1.05162e-06</v>
+      </c>
+      <c r="L2" s="2">
+        <f>IF(COUNT('Turns'!F6,'Turns'!F24)=2,SUM('Turns'!F6,'Turns'!F24),"Unknown")</f>
+        <v>1.2e-06</v>
+      </c>
+      <c r="M2" s="2">
         <f>IF(COUNT('Turns'!D5,'Turns'!D23)=2,SUM('Turns'!D5,'Turns'!D23),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="K2" s="2">
+        <v>4681.0</v>
+      </c>
+      <c r="N2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E23)=2,SUM('Turns'!E5,'Turns'!E23),"Unknown")</f>
-        <v>1.046844e-06</v>
-      </c>
-      <c r="L2" s="2">
+        <v>8.2043887e-05</v>
+      </c>
+      <c r="O2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F23)=2,SUM('Turns'!F5,'Turns'!F23),"Unknown")</f>
-        <v>1.2e-06</v>
-      </c>
-      <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>2307.0</v>
-      </c>
-      <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>4.02511518e-05</v>
-      </c>
-      <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.614e-05</v>
+        <v>9.362e-05</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D9,'Turns'!D25)=2,SUM('Turns'!D9,'Turns'!D25),"Unknown")</f>
-        <v>2374.0</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E9,'Turns'!E25)=2,SUM('Turns'!E9,'Turns'!E25),"Unknown")</f>
-        <v>0.000517751595</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F9,'Turns'!F25)=2,SUM('Turns'!F9,'Turns'!F25),"Unknown")</f>
-        <v>0.0005935</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D28)=2,SUM('Turns'!D13,'Turns'!D28),"Unknown")</f>
-        <v>53.0</v>
+        <f>IF(COUNT('Turns'!D14,'Turns'!D29)=2,SUM('Turns'!D14,'Turns'!D29),"Unknown")</f>
+        <v>48.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
-        <v>5.5482732e-05</v>
+        <f>IF(COUNT('Turns'!E14,'Turns'!E29)=2,SUM('Turns'!E14,'Turns'!E29),"Unknown")</f>
+        <v>5.047776e-05</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
-        <v>6.36e-05</v>
+        <f>IF(COUNT('Turns'!F14,'Turns'!F29)=2,SUM('Turns'!F14,'Turns'!F29),"Unknown")</f>
+        <v>5.76e-05</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>9.46458e-06</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006239539188</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E33)=2,SUM('Turns'!E18,'Turns'!E33),"Unknown")</f>
+        <v>0.000143037847</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00071524</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F33)=2,SUM('Turns'!F18,'Turns'!F33),"Unknown")</f>
+        <v>0.00016322</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>14.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>72.0</v>
+        <v>16.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>4456.8</v>
+        <v>3184.496</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>126</v>
@@ -1763,7 +1752,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>128</v>
@@ -1775,7 +1764,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>130</v>
@@ -1795,7 +1784,7 @@
         <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>132</v>
@@ -1807,80 +1796,80 @@
         <v>49</v>
       </c>
       <c r="J4" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K4" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L4" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M4" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K4" s="2">
+        <v>2307.0</v>
+      </c>
+      <c r="N4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L4" s="2">
+        <v>4.0434789e-05</v>
+      </c>
+      <c r="O4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M4" s="2">
+        <v>4.614e-05</v>
+      </c>
+      <c r="P4" s="2">
         <v>0</v>
       </c>
-      <c r="N4" s="2">
+      <c r="Q4" s="2">
         <v>0</v>
       </c>
-      <c r="O4" s="2">
+      <c r="R4" s="2">
         <v>0</v>
       </c>
-      <c r="P4" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2307.0</v>
-      </c>
-      <c r="Q4" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.0005031393975</v>
-      </c>
-      <c r="R4" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00057675</v>
-      </c>
       <c r="S4" s="2">
+        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <v>28.0</v>
+      </c>
+      <c r="T4" s="2">
+        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
+        <v>2.944536e-05</v>
+      </c>
+      <c r="U4" s="2">
+        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <v>3.36e-05</v>
+      </c>
+      <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>28.0</v>
-      </c>
-      <c r="T4" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>2.9311632e-05</v>
-      </c>
-      <c r="U4" s="2">
+        <v>9.46458e-06</v>
+      </c>
+      <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.36e-05</v>
-      </c>
-      <c r="V4" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="W4" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.421596e-06</v>
-      </c>
-      <c r="X4" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0005423960475</v>
+        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
+        <v>7.9870539e-05</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00062175</v>
+        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
+        <v>9.114e-05</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>54.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>9.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>2607.991</v>
+        <v>1712.943</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>126</v>
@@ -1900,7 +1889,7 @@
         <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F5" s="1">
         <v>2310</v>
@@ -1915,83 +1904,83 @@
         <v>133</v>
       </c>
       <c r="J5" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K5" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L5" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K5" s="2">
+        <v>2307.0</v>
+      </c>
+      <c r="N5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L5" s="2">
+        <v>4.0434789e-05</v>
+      </c>
+      <c r="O5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M5" s="2">
+        <v>4.614e-05</v>
+      </c>
+      <c r="P5" s="2">
         <v>0</v>
       </c>
-      <c r="N5" s="2">
+      <c r="Q5" s="2">
         <v>0</v>
       </c>
-      <c r="O5" s="2">
+      <c r="R5" s="2">
         <v>0</v>
       </c>
-      <c r="P5" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2307.0</v>
-      </c>
-      <c r="Q5" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.0005031393975</v>
-      </c>
-      <c r="R5" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00057675</v>
-      </c>
       <c r="S5" s="2">
+        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <v>28.0</v>
+      </c>
+      <c r="T5" s="2">
+        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
+        <v>2.944536e-05</v>
+      </c>
+      <c r="U5" s="2">
+        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <v>3.36e-05</v>
+      </c>
+      <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>28.0</v>
-      </c>
-      <c r="T5" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>2.9311632e-05</v>
-      </c>
-      <c r="U5" s="2">
+        <v>9.46458e-06</v>
+      </c>
+      <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.36e-05</v>
-      </c>
-      <c r="V5" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="W5" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.421596e-06</v>
-      </c>
-      <c r="X5" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.0005423960475</v>
+        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
+        <v>7.9870539e-05</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00062175</v>
+        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
+        <v>9.114e-05</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>54.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>9.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>2601.198</v>
+        <v>1705.743</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>137</v>
@@ -2011,7 +2000,7 @@
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>139</v>
@@ -2023,7 +2012,7 @@
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>42.343</v>
+        <v>46.121</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>130</v>
@@ -2043,19 +2032,19 @@
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>143</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I7" t="s">
         <v>140</v>
       </c>
       <c r="AD7" s="1">
-        <v>40.041</v>
+        <v>43.834</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>130</v>
@@ -2075,7 +2064,7 @@
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>132</v>
@@ -2087,52 +2076,49 @@
         <v>49</v>
       </c>
       <c r="J8" s="2">
+        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K8" s="2">
+        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L8" s="2">
+        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M8" s="2">
         <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K8" s="2">
+        <v>2374.0</v>
+      </c>
+      <c r="N8" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L8" s="2">
+        <v>4.1609098e-05</v>
+      </c>
+      <c r="O8" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>2307.0</v>
-      </c>
-      <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>4.02511518e-05</v>
-      </c>
-      <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.614e-05</v>
+        <v>4.748e-05</v>
       </c>
       <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>67.0</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>1.46121975e-05</v>
+        <v>0</v>
       </c>
       <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>1.675e-05</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>25.0</v>
+        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <v>20.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.61711e-05</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>2.10324e-05</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>3e-05</v>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>2.4e-05</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
@@ -2144,23 +2130,23 @@
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>8.15578713e-05</v>
+        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
+        <v>6.3167308e-05</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>9.349e-05</v>
+        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
+        <v>7.208e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>1801.011</v>
+        <v>1419.193</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>126</v>
@@ -2180,7 +2166,7 @@
         <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F9" s="1">
         <v>2377</v>
@@ -2189,58 +2175,55 @@
         <v>136</v>
       </c>
       <c r="H9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I9" t="s">
         <v>144</v>
       </c>
       <c r="J9" s="2">
+        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K9" s="2">
+        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
+        <v>5.2581e-07</v>
+      </c>
+      <c r="L9" s="2">
+        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M9" s="2">
         <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K9" s="2">
+        <v>2374.0</v>
+      </c>
+      <c r="N9" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L9" s="2">
+        <v>4.1609098e-05</v>
+      </c>
+      <c r="O9" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M9" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>2307.0</v>
-      </c>
-      <c r="N9" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>4.02511518e-05</v>
-      </c>
-      <c r="O9" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.614e-05</v>
+        <v>4.748e-05</v>
       </c>
       <c r="P9" s="2">
-        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>67.0</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2">
-        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>1.46121975e-05</v>
+        <v>0</v>
       </c>
       <c r="R9" s="2">
-        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>1.675e-05</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>25.0</v>
+        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <v>20.0</v>
       </c>
       <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.61711e-05</v>
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>2.10324e-05</v>
       </c>
       <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>3e-05</v>
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>2.4e-05</v>
       </c>
       <c r="V9" s="2">
         <v>0</v>
@@ -2252,26 +2235,26 @@
         <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>8.15578713e-05</v>
+        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
+        <v>6.3167308e-05</v>
       </c>
       <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>9.349e-05</v>
+        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
+        <v>7.208e-05</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AD9" s="1">
-        <v>1797.868</v>
+        <v>1414.176</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>137</v>
@@ -2329,7 +2312,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/shell_script/report.xlsx
+++ b/reports/shell_script/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="145">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d142-4fb9-74b1-9161-3e9286297f58</t>
+    <t>01a0d587-42ef-7a82-aea6-fa40a1fdab08</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-24T02:09:35.117183Z</t>
+    <t>2026-09-24T22:21:31.719587Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0d142-4fc4-7743-8b54-9fbce1d8ddab</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
+    <t>01a0d587-42f8-7413-8109-860b31181b3c</t>
   </si>
   <si>
     <t>Input at standard rate</t>
@@ -353,8 +350,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_056f2f78f65d105c006ab48bdc549c87d2ba63244a0418f912", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIvca-dztntiyaCCQTmPZ7cet6acr5BMOlGTEjxa1kMiyCRnLbg_hLHVSizBsjibwMS05hjhM9yIRJsdJWwYjgUgxAs_pG5zSX6XyKUJuUD5Hl3NecqcHtnLCvISyzM0oc28MZNP0C9YMFG9WAsIDdJBIeNBWojWm_yueEKhFQKFFfjRneUea_IRcnF-GbYm4Z5YX1xKX_wicLYUZ_54iItcAzog3JWM1U8zSOfabQS-AeJOE2CxRiwQy9PccIzIv5tdd74YNSwtvOJY9QwqZVaVL7esJM0x7k5HTjM9o2WtCviAfZtp0U-8i_p4xhztFE4gwE_x6oOKvkiHOZI-WwT66d_An53eXb-lHYl5pdewp3vRn1lEPeE9gtwzhHh6Mf0ckbczy1EaaTk4QWmtr7dk1xHr8aVDh7o_2xjLOunauEW9RyopaLiKR1R_hXYHJUUSAMnMW5to55nd7ESQX11fOBgO31JvoxVXLJy1lW829OdzQ4MPPQjOpzJHezSvgNnBNfcWtMn2v-Iu0d1QWfbreq9gTvYSIabbtQIcFxUaae-sDWBnRUvVKsIFknV85srM9CBP1tEQBIfCQCe0wjP0IJ0lrAI8272gkGt0hjzByHpq6Q9Lld0CLTIKYgeWHl4d9SdgSHSRVPblTfzGSsMfcQaJq41vNMyhY5NOFZVW-BdpHnuhvpEsu3ZsEOfmg8Yg2NZl7iL9qmzAyONwozFhvRWArKfpscEAmmznxhhJmeMFVkcBThyVMALAtSl-nJGWW8mgx5I2d2Wla3WdYJMOlKoDC9iQucjiLouvrAEnezPXBiIhqJSkcxbs7Kgg8bfb170cwqbT7YnOS76nRR2RwH2kkeCJYhrgK_9YLncVIAKFLUNg1RGCeGd4KggzrsOSON9qbmbNzRRfOdmEqcTMo2KKigtjvOpGMmA1IadP4n1b-ogstLuS76OPuQH6HBNOVpMj-BRIz3VkmZocFxqMsbWp05cC_Ym6d0hFHm7ofgeGRegPlsROmag3N42YE8i_t414WkcWcQpAoPqFw3O73Yt1Eq_1HbZodCBwJEDueoGpk3U_md6gIWGxFyd7PHnHgrWn8wVIMAaVMJcvLplmY6emxH7Tx-S30kJUTFJtEmLObLgTc86DJ6TXQPKu-WKWq_80rmpexw46AHRnIUJhhHIpm4TLH2pXb94I1F_fyUzAduVyupGX82wJ-sxHEtIt"}, {"type": "function_call", "name": "execute", "arguments": "{\"command\":\"sh ./summarize.sh\",\"timeout\":120}", "call_id": "call_PlpK37RsthN7RecjgOhp11pw", "id": "fc_056f2f78f65d105c006ab48bdc717087d29ed744442d3d816a", "index": 1}]
-{"name": "execute", "args": {"command": "sh ./summarize.sh", "timeout": 120}, "id": "call_PlpK37RsthN7RecjgOhp11pw", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0305eb8a54a04ee3006ab5a3a755cc87d28c9ebc14ca0f7992", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaOn2Vx__1CqeTA9UhRWq69sE5va7D4fs9q0zuF2RJNMYiEG23WSCKXy9y0NI3BRyfzeW62j3zjIOWc9ZF1XT9VkeE-xf-6vhR-sUv5n4VuwxQiuWvC96ea_LIljgPujnRNo2J-iV4Uu-pr6MlSAtGinpam70lNGhIePlwgKD_Y11hLy6pkLoQOkOApFENuaiMF09HRKMicQRurilDr0rPf1tnx6zgQYAn677RO1aXdscnv4qA46fhitGsizysVUNA5T7Jj0EWT0XqdMhnOwVY08ugHV9hE2pH1xa1r7XxnMS6_UbbY4Ul6h5sC-4iV-771J3mF25FbeVR7GusmPqCE4dKgJ0OYRQizyoegsJjKkNCAf3voNWY3Zow6SLJHn5D1-Kz1kzU9wvcrY8iSsHkm09XhpEKHwavVyhvkWjcjxPRHRZaIPRaMQKj5Jwz9Uvdhn_EngNHCnuLJHUVlYGPtd8N7ZCh5gBG7OqTw-giWnJ7gTx8p2GzyiJTmQCJG0pj5q6DYLeic8Lonjn-V-p2Cyqiqdu2GWy2YwNxyI0AtAccFzKfZ4LkIaQvjL32KTsC2emlfZlmNV-s1Y3Io_pk6joInlAwAw7XIIIC--MGOmtYkTcjImcj4qW33qY0klEBK8VtjuAHOi1uAixbz9-F2Dr6gvTIuZPzk13OCBUVoEA-VtKCXIEe-7BCL_AsBU1vJKIydCdl7C-lVWwARaubX1kZnJD8V9-C7XgeG-8TRueyKyOOXTKvAgOPwxszbOjLWORCExvXDLWgb6bRBZ0QHdqR8I4pmP3VP4PA15yT-Xu-i2GV6UHdGrULMbosaLjpwnJljzACCEK6NOlkhPqSIlp8rlkgNKEk1Ai4DaACPtr697mT1fiCbQgmejxpp4j1YqsnAKktYxnmbagg4YmCkFuPyCRsDb2JgW8QG2lJLUO6-fW5IaatmMoKBgFWZNXbnLDBMBD9DG2q5VU51NXUYk84fmvBRwggDIWIq-zeeuLo8jeN28Mi2gGwrbrt0CWz0yMddkUGic383qJT0UB5rpLTyz9EkORKv8HVF2uoXA5DiAN5Db1VWsKNeNEGYTTuj4JMRto_TTaIC5BYPSYSz1bjYeNw64g0SvGRRjfW5rmrEi0UOOikr8OFLRiQ4BTxPhj9pQXJnU9hr2kUgIASDGd-QL-ITv0hVZNDF0Kv25ElAz4kkRPyqb151rgIyxzOWG"}, {"type": "function_call", "name": "execute", "arguments": "{\"command\":\"sh ./summarize.sh\",\"timeout\":120}", "call_id": "call_UhZPcsWNlrqTM86fvtiZZuIF", "id": "fc_0305eb8a54a04ee3006ab5a3a77a9887d2898254c46a853836", "index": 1}]
+{"name": "execute", "args": {"command": "sh ./summarize.sh", "timeout": 120}, "id": "call_UhZPcsWNlrqTM86fvtiZZuIF", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -366,7 +363,7 @@
     <t>Tool · execute</t>
   </si>
   <si>
-    <t>01a0d142-5671-7cd2-b611-d236227197e9</t>
+    <t>01a0d587-4733-7281-936a-e7b34c0438ff</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -386,13 +383,16 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0d142-56a2-7893-85da-b7289e7433ba</t>
+    <t>01a0d587-4750-7b32-ad48-53449c4e54b6</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "Orders: 3  \nTotal units: 9  \n\nExit status: 0", "phase": "final_answer", "index": 0, "id": "msg_056f2f78f65d105c006ab48bddd1ec87d2924ce6407aa49bd2"}]</t>
+    <t>[{"type": "text", "text": "Orders: 3  \nTotal units: 9  \n\nExit status: 0", "phase": "final_answer", "index": 0, "id": "msg_0305eb8a54a04ee3006ab5a3a8587487d29bf4cf5a0efbfa68"}]</t>
   </si>
   <si>
     <t>shell_agent</t>
@@ -413,7 +413,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0d142-4fbd-7501-913f-6095a96d4f11</t>
+    <t>01a0d587-42f2-7a62-b6bb-a43ef2a73202</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -425,7 +425,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d142-4fbe-7f61-9336-1195e0309092</t>
+    <t>01a0d587-42f3-7e71-b2d4-6e6610c51eb3</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -446,7 +446,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0d142-5670-7ae0-8d3e-e5377d43b493</t>
+    <t>01a0d587-4732-7661-be25-1701b031358e</t>
   </si>
   <si>
     <t xml:space="preserve">        execute</t>
@@ -466,7 +466,7 @@
 Only available on backends implementing SandboxBackendProtocol; otherwise it returns an error.</t>
   </si>
   <si>
-    <t>01a0d142-569f-7521-8050-9fa794f475af</t>
+    <t>01a0d587-474e-7bb2-9895-90f97a30614a</t>
   </si>
 </sst>
 </file>
@@ -873,7 +873,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -933,20 +933,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E33)=2,SUM('Turns'!E18,'Turns'!E33),"Unknown")</f>
-        <v>0.000143037847</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
+        <v>0.0006239467976</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F33)=2,SUM('Turns'!F18,'Turns'!F33),"Unknown")</f>
-        <v>0.00016322</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
+        <v>0.00070924</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>62.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -957,20 +957,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E33)=2,SUM('Turns'!E18,'Turns'!E33),"Unknown")</f>
-        <v>0.000143037847</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
+        <v>0.0006239467976</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F33)=2,SUM('Turns'!F18,'Turns'!F33),"Unknown")</f>
-        <v>0.00016322</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
+        <v>0.00070924</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>62.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1004,23 +1004,23 @@
         <v>97</v>
       </c>
       <c r="D5" s="5">
-        <v>2307</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.0434789e-05</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.614e-05</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
@@ -1033,27 +1033,8 @@
       <c r="C6" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="5">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2">
-        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F6" s="2">
-        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="5">
-        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" customHeight="1">
+    </row>
+    <row r="7" spans="1:13" ht="73" customHeight="1">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -1063,8 +1044,11 @@
       <c r="C7" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="73" customHeight="1">
+      <c r="I7" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -1072,10 +1056,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
@@ -1086,10 +1070,26 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="6" t="s">
         <v>103</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2307</v>
+      </c>
+      <c r="E9" s="2">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000507390045</v>
+      </c>
+      <c r="F9" s="2">
+        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>0.00057675</v>
+      </c>
+      <c r="G9" s="5">
+        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>51.0</v>
+      </c>
+      <c r="H9" s="5">
+        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>58.0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
@@ -1103,29 +1103,48 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="24" customHeight="1">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="D11" s="4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="24" customHeight="1">
+      <c r="A12" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="4">
-        <v>37</v>
+      <c r="D12" s="5">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
+        <v>9.501192e-06</v>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>1.08e-05</v>
+      </c>
+      <c r="G12" s="5">
+        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="5">
+        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1139,26 +1158,26 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>2.9559264e-05</v>
       </c>
       <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!F17),D13*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.08e-05</v>
+        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>3.36e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="24" customHeight="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="281" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1168,27 +1187,11 @@
       <c r="C14" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="5">
-        <v>28</v>
-      </c>
-      <c r="E14" s="2">
-        <f>IF(AND(ISNUMBER(F14),ISNUMBER('Reference data'!$B$3)),F14*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.944536e-05</v>
-      </c>
-      <c r="F14" s="2">
-        <f>IF(D14=0,0,IF(ISNUMBER('Reference data'!E17),D14*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.36e-05</v>
-      </c>
-      <c r="G14" s="5">
-        <f>IF(ISNUMBER(E14),ROUND(E14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H14" s="5">
-        <f>IF(ISNUMBER(F14),ROUND(F14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="281" customHeight="1">
+      <c r="I14" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="24" customHeight="1">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -1196,10 +1199,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="24" customHeight="1">
@@ -1213,106 +1213,125 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="24" customHeight="1">
-      <c r="A17" t="s">
+    <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>105</v>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13)=4,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13),"Unknown")</f>
+        <v>0.000546978345</v>
+      </c>
+      <c r="F17" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13)=4,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13),"Unknown")</f>
+        <v>0.00062175</v>
+      </c>
+      <c r="G17" s="5">
+        <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>55.0</v>
+      </c>
+      <c r="H17" s="5">
+        <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>62.0</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="B18" s="4">
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E18" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14)=4,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14),"Unknown")</f>
-        <v>7.9870539e-05</v>
-      </c>
-      <c r="F18" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14)=4,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14),"Unknown")</f>
-        <v>9.114e-05</v>
-      </c>
-      <c r="G18" s="5">
-        <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="H18" s="5">
-        <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B19" s="4">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="M18" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M19" s="4" t="s">
+    </row>
+    <row r="19" spans="1:13" ht="24" customHeight="1">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="24" customHeight="1">
+      <c r="I19" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="60" customHeight="1">
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="60" customHeight="1">
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
         <v>117</v>
       </c>
-      <c r="I21" s="6" t="s">
+    </row>
+    <row r="21" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A22" s="4" t="s">
+      <c r="B21" s="4">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2377</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M21" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="4">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2377</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M22" s="4" t="s">
+    </row>
+    <row r="22" spans="1:13" ht="24" customHeight="1">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
         <v>120</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2307</v>
+      </c>
+      <c r="E22" s="2">
+        <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.05912036e-05</v>
+      </c>
+      <c r="F22" s="2">
+        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!C17),D22*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.614e-05</v>
+      </c>
+      <c r="G22" s="5">
+        <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H22" s="5">
+        <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1321,72 +1340,72 @@
         <v>97</v>
       </c>
       <c r="D23" s="5">
-        <v>2374</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
         <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.1609098e-05</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F23" s="2">
-        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!C17),D23*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.748e-05</v>
+        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!B17),D23*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G23" s="5">
         <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H23" s="5">
         <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="24" customHeight="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="60" customHeight="1">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="5">
-        <v>3</v>
-      </c>
-      <c r="E24" s="2">
-        <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="F24" s="2">
-        <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!B17),D24*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G24" s="5">
-        <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="5">
-        <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="60" customHeight="1">
+        <v>121</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="24" customHeight="1">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>118</v>
+        <v>103</v>
+      </c>
+      <c r="D25" s="5">
+        <v>67</v>
+      </c>
+      <c r="E25" s="2">
+        <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.4735645e-05</v>
+      </c>
+      <c r="F25" s="2">
+        <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!D17),D25*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>1.675e-05</v>
+      </c>
+      <c r="G25" s="5">
+        <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H25" s="5">
+        <f>IF(ISNUMBER(F25),ROUND(F25*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="24" customHeight="1">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1395,34 +1414,53 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="24" customHeight="1">
-      <c r="A27" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
+    <row r="27" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="4">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="4">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="4">
+      <c r="D27" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="24" customHeight="1">
+    <row r="28" spans="1:13" ht="24" customHeight="1">
+      <c r="A28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="5">
+        <v>20</v>
+      </c>
+      <c r="E28" s="2">
+        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.111376e-05</v>
+      </c>
+      <c r="F28" s="2">
+        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.4e-05</v>
+      </c>
+      <c r="G28" s="5">
+        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H28" s="5">
+        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="47" customHeight="1">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1430,43 +1468,24 @@
       <c r="C29" t="s">
         <v>108</v>
       </c>
-      <c r="D29" s="5">
-        <v>20</v>
-      </c>
-      <c r="E29" s="2">
-        <f>IF(AND(ISNUMBER(F29),ISNUMBER('Reference data'!$B$3)),F29*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.10324e-05</v>
-      </c>
-      <c r="F29" s="2">
-        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!E17),D29*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.4e-05</v>
-      </c>
-      <c r="G29" s="5">
-        <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H29" s="5">
-        <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="47" customHeight="1">
+      <c r="I29" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="24" customHeight="1">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1475,49 +1494,38 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="24" customHeight="1">
-      <c r="A32" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="s">
+    <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="4">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="2">
+        <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28)=4,SUM('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28),"Unknown")</f>
+        <v>7.69684526e-05</v>
+      </c>
+      <c r="F32" s="2">
+        <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28)=4,SUM('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28),"Unknown")</f>
+        <v>8.749e-05</v>
+      </c>
+      <c r="G32" s="5">
+        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="H32" s="5">
+        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E33" s="2">
-        <f>IF(COUNT('Turns'!E23,'Turns'!E24,'Turns'!E29)=3,SUM('Turns'!E23,'Turns'!E24,'Turns'!E29),"Unknown")</f>
-        <v>6.3167308e-05</v>
-      </c>
-      <c r="F33" s="2">
-        <f>IF(COUNT('Turns'!F23,'Turns'!F24,'Turns'!F29)=3,SUM('Turns'!F23,'Turns'!F24,'Turns'!F29),"Unknown")</f>
-        <v>7.208e-05</v>
-      </c>
-      <c r="G33" s="5">
-        <f>IF(ISNUMBER(E33),ROUND(E33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="H33" s="5">
-        <f>IF(ISNUMBER(F33),ROUND(F33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>112</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE33">
+  <conditionalFormatting sqref="A2:AE32">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1650,7 +1658,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>125</v>
@@ -1659,80 +1667,83 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D6,'Turns'!D24)=2,SUM('Turns'!D6,'Turns'!D24),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D23)=2,SUM('Turns'!D5,'Turns'!D23),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E6,'Turns'!E24)=2,SUM('Turns'!E6,'Turns'!E24),"Unknown")</f>
-        <v>1.05162e-06</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E23)=2,SUM('Turns'!E5,'Turns'!E23),"Unknown")</f>
+        <v>1.055688e-06</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F6,'Turns'!F24)=2,SUM('Turns'!F6,'Turns'!F24),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F23)=2,SUM('Turns'!F5,'Turns'!F23),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D23)=2,SUM('Turns'!D5,'Turns'!D23),"Unknown")</f>
-        <v>4681.0</v>
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>2307.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E23)=2,SUM('Turns'!E5,'Turns'!E23),"Unknown")</f>
-        <v>8.2043887e-05</v>
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>4.05912036e-05</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F23)=2,SUM('Turns'!F5,'Turns'!F23),"Unknown")</f>
-        <v>9.362e-05</v>
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>4.614e-05</v>
       </c>
       <c r="P2" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D9,'Turns'!D25)=2,SUM('Turns'!D9,'Turns'!D25),"Unknown")</f>
+        <v>2374.0</v>
       </c>
       <c r="Q2" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E9,'Turns'!E25)=2,SUM('Turns'!E9,'Turns'!E25),"Unknown")</f>
+        <v>0.00052212569</v>
       </c>
       <c r="R2" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F9,'Turns'!F25)=2,SUM('Turns'!F9,'Turns'!F25),"Unknown")</f>
+        <v>0.0005935</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D14,'Turns'!D29)=2,SUM('Turns'!D14,'Turns'!D29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D13,'Turns'!D28)=2,SUM('Turns'!D13,'Turns'!D28),"Unknown")</f>
         <v>48.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E14,'Turns'!E29)=2,SUM('Turns'!E14,'Turns'!E29),"Unknown")</f>
-        <v>5.047776e-05</v>
+        <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
+        <v>5.0673024e-05</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F14,'Turns'!F29)=2,SUM('Turns'!F14,'Turns'!F29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
         <v>5.76e-05</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>9.501192e-06</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E33)=2,SUM('Turns'!E18,'Turns'!E33),"Unknown")</f>
-        <v>0.000143037847</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
+        <v>0.0006239467976</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F33)=2,SUM('Turns'!F18,'Turns'!F33),"Unknown")</f>
-        <v>0.00016322</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
+        <v>0.00070924</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>62.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>71.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>3184.496</v>
+        <v>2045.869</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>126</v>
@@ -1752,7 +1763,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>128</v>
@@ -1764,7 +1775,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.427</v>
+        <v>0.394</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>130</v>
@@ -1784,7 +1795,7 @@
         <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>132</v>
@@ -1796,80 +1807,80 @@
         <v>49</v>
       </c>
       <c r="J4" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K4" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L4" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M4" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
         <v>2307.0</v>
       </c>
-      <c r="N4" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>4.0434789e-05</v>
-      </c>
-      <c r="O4" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>4.614e-05</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
       <c r="Q4" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
+        <v>0.000507390045</v>
       </c>
       <c r="R4" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
+        <v>0.00057675</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
         <v>28.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>2.944536e-05</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>2.9559264e-05</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
         <v>3.36e-05</v>
       </c>
       <c r="V4" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W4" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>9.501192e-06</v>
       </c>
       <c r="X4" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>7.9870539e-05</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>0.000546978345</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>9.114e-05</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>0.00062175</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>55.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>62.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>1712.943</v>
+        <v>1085.967</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>126</v>
@@ -1889,7 +1900,7 @@
         <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F5" s="1">
         <v>2310</v>
@@ -1904,83 +1915,83 @@
         <v>133</v>
       </c>
       <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M5" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
         <v>2307.0</v>
       </c>
-      <c r="N5" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>4.0434789e-05</v>
-      </c>
-      <c r="O5" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>4.614e-05</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
       <c r="Q5" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
+        <v>0.000507390045</v>
       </c>
       <c r="R5" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
+        <v>0.00057675</v>
       </c>
       <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
         <v>28.0</v>
       </c>
       <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>2.944536e-05</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>2.9559264e-05</v>
       </c>
       <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
         <v>3.36e-05</v>
       </c>
       <c r="V5" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
         <v>9.0</v>
       </c>
       <c r="W5" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>9.501192e-06</v>
       </c>
       <c r="X5" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
         <v>1.08e-05</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>7.9870539e-05</v>
+        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
+        <v>0.000546978345</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>9.114e-05</v>
+        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
+        <v>0.00062175</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
+        <v>55.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>62.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>1705.743</v>
+        <v>1079.331</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>137</v>
@@ -2000,7 +2011,7 @@
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>139</v>
@@ -2012,7 +2023,7 @@
         <v>49</v>
       </c>
       <c r="AD6" s="1">
-        <v>46.121</v>
+        <v>27.424</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>130</v>
@@ -2032,19 +2043,19 @@
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>143</v>
       </c>
       <c r="H7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I7" t="s">
         <v>140</v>
       </c>
       <c r="AD7" s="1">
-        <v>43.834</v>
+        <v>25.297</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>130</v>
@@ -2064,7 +2075,7 @@
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>132</v>
@@ -2076,48 +2087,51 @@
         <v>49</v>
       </c>
       <c r="J8" s="2">
-        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K8" s="2">
-        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L8" s="2">
-        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>2374.0</v>
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>2307.0</v>
       </c>
       <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>4.1609098e-05</v>
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>4.05912036e-05</v>
       </c>
       <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.748e-05</v>
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>4.614e-05</v>
       </c>
       <c r="P8" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
+        <v>67.0</v>
       </c>
       <c r="Q8" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
+        <v>1.4735645e-05</v>
       </c>
       <c r="R8" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
+        <v>1.675e-05</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
         <v>20.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>2.10324e-05</v>
+        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
+        <v>2.111376e-05</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
         <v>2.4e-05</v>
       </c>
       <c r="V8" s="2">
@@ -2130,23 +2144,23 @@
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
-        <v>6.3167308e-05</v>
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>7.69684526e-05</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
-        <v>7.208e-05</v>
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>8.749e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>1419.193</v>
+        <v>926.0700000000001</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>126</v>
@@ -2166,7 +2180,7 @@
         <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F9" s="1">
         <v>2377</v>
@@ -2175,54 +2189,57 @@
         <v>136</v>
       </c>
       <c r="H9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I9" t="s">
         <v>144</v>
       </c>
       <c r="J9" s="2">
-        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K9" s="2">
-        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
+        <v>5.27844e-07</v>
       </c>
       <c r="L9" s="2">
-        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M9" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>2374.0</v>
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>2307.0</v>
       </c>
       <c r="N9" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>4.1609098e-05</v>
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>4.05912036e-05</v>
       </c>
       <c r="O9" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>4.748e-05</v>
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>4.614e-05</v>
       </c>
       <c r="P9" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
+        <v>67.0</v>
       </c>
       <c r="Q9" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
+        <v>1.4735645e-05</v>
       </c>
       <c r="R9" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
+        <v>1.675e-05</v>
       </c>
       <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
         <v>20.0</v>
       </c>
       <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>2.10324e-05</v>
+        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
+        <v>2.111376e-05</v>
       </c>
       <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
         <v>2.4e-05</v>
       </c>
       <c r="V9" s="2">
@@ -2235,26 +2252,26 @@
         <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
-        <v>6.3167308e-05</v>
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>7.69684526e-05</v>
       </c>
       <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
-        <v>7.208e-05</v>
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>8.749e-05</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB9" s="5">
         <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AD9" s="1">
-        <v>1414.176</v>
+        <v>922.1950000000001</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>137</v>
@@ -2312,7 +2329,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87635</v>
+        <v>0.87974</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/shell_script/report.xlsx
+++ b/reports/shell_script/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="172">
   <si>
     <t>Request</t>
   </si>
@@ -165,13 +165,13 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d587-42ef-7a82-aea6-fa40a1fdab08</t>
+    <t>01a1143f-93d5-79a1-85dd-05eee1ff9487</t>
   </si>
   <si>
     <t>Recording</t>
   </si>
   <si>
-    <t>Provider trace</t>
+    <t>Offline simulation</t>
   </si>
   <si>
     <t>FX reference date</t>
@@ -216,7 +216,7 @@
     <t>Pricing scope</t>
   </si>
   <si>
-    <t>Standard online token rates. Verify rates and model access before use. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. No batch, regional, long-context, tool, or negotiated pricing adjustments are applied.</t>
+    <t>Published online token rates verified 2026-10-05. Copilot uses GitHub rates, including saved long-context tiers, before plan allowances; these are usage estimates, not subscription invoices. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. Direct OpenAI and Anthropic entries use standard rates; no batch, regional, tool, negotiated, or unrecorded context-tier adjustments are applied. Model availability and context capacity require separate verification.</t>
   </si>
   <si>
     <t>Model</t>
@@ -252,7 +252,7 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>2026-09-18</t>
+    <t>2026-10-05</t>
   </si>
   <si>
     <t>https://developers.openai.com/api/docs/models/gpt-5.5.md</t>
@@ -291,6 +291,99 @@
     <t>Illustrative demo rates based on openai:gpt-5.6-luna; no provider billing</t>
   </si>
   <si>
+    <t>anthropic:claude-haiku-4-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-haiku-4-5-20251001</t>
+  </si>
+  <si>
+    <t>anthropic:claude-opus-5-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-4-6</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-5-5</t>
+  </si>
+  <si>
+    <t>copilot:claude-haiku-4.5</t>
+  </si>
+  <si>
+    <t>https://docs.github.com/en/copilot/reference/copilot-billing/models-and-pricing</t>
+  </si>
+  <si>
+    <t>copilot:claude-opus-5.5</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-4.6</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-5.5</t>
+  </si>
+  <si>
+    <t>copilot:gemini-3.8-flash</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.3-codex</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-astra.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-luna.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-sol.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6.1-sol.md</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4 [long context]</t>
+  </si>
+  <si>
+    <t>Above 272,000 input tokens</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol [long context]</t>
+  </si>
+  <si>
     <t>Run total</t>
   </si>
   <si>
@@ -303,10 +396,10 @@
     <t>LLM request</t>
   </si>
   <si>
-    <t>gpt-5.6-luna</t>
-  </si>
-  <si>
-    <t>01a0d587-42f8-7413-8109-860b31181b3c</t>
+    <t>scripted-chat</t>
+  </si>
+  <si>
+    <t>01a1143f-93da-7e33-b991-06e60a74ba5a</t>
   </si>
   <si>
     <t>Input at standard rate</t>
@@ -341,17 +434,13 @@
     <t>LLM response</t>
   </si>
   <si>
-    <t>Reasoning</t>
-  </si>
-  <si>
     <t>Output</t>
   </si>
   <si>
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0305eb8a54a04ee3006ab5a3a755cc87d28c9ebc14ca0f7992", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaOn2Vx__1CqeTA9UhRWq69sE5va7D4fs9q0zuF2RJNMYiEG23WSCKXy9y0NI3BRyfzeW62j3zjIOWc9ZF1XT9VkeE-xf-6vhR-sUv5n4VuwxQiuWvC96ea_LIljgPujnRNo2J-iV4Uu-pr6MlSAtGinpam70lNGhIePlwgKD_Y11hLy6pkLoQOkOApFENuaiMF09HRKMicQRurilDr0rPf1tnx6zgQYAn677RO1aXdscnv4qA46fhitGsizysVUNA5T7Jj0EWT0XqdMhnOwVY08ugHV9hE2pH1xa1r7XxnMS6_UbbY4Ul6h5sC-4iV-771J3mF25FbeVR7GusmPqCE4dKgJ0OYRQizyoegsJjKkNCAf3voNWY3Zow6SLJHn5D1-Kz1kzU9wvcrY8iSsHkm09XhpEKHwavVyhvkWjcjxPRHRZaIPRaMQKj5Jwz9Uvdhn_EngNHCnuLJHUVlYGPtd8N7ZCh5gBG7OqTw-giWnJ7gTx8p2GzyiJTmQCJG0pj5q6DYLeic8Lonjn-V-p2Cyqiqdu2GWy2YwNxyI0AtAccFzKfZ4LkIaQvjL32KTsC2emlfZlmNV-s1Y3Io_pk6joInlAwAw7XIIIC--MGOmtYkTcjImcj4qW33qY0klEBK8VtjuAHOi1uAixbz9-F2Dr6gvTIuZPzk13OCBUVoEA-VtKCXIEe-7BCL_AsBU1vJKIydCdl7C-lVWwARaubX1kZnJD8V9-C7XgeG-8TRueyKyOOXTKvAgOPwxszbOjLWORCExvXDLWgb6bRBZ0QHdqR8I4pmP3VP4PA15yT-Xu-i2GV6UHdGrULMbosaLjpwnJljzACCEK6NOlkhPqSIlp8rlkgNKEk1Ai4DaACPtr697mT1fiCbQgmejxpp4j1YqsnAKktYxnmbagg4YmCkFuPyCRsDb2JgW8QG2lJLUO6-fW5IaatmMoKBgFWZNXbnLDBMBD9DG2q5VU51NXUYk84fmvBRwggDIWIq-zeeuLo8jeN28Mi2gGwrbrt0CWz0yMddkUGic383qJT0UB5rpLTyz9EkORKv8HVF2uoXA5DiAN5Db1VWsKNeNEGYTTuj4JMRto_TTaIC5BYPSYSz1bjYeNw64g0SvGRRjfW5rmrEi0UOOikr8OFLRiQ4BTxPhj9pQXJnU9hr2kUgIASDGd-QL-ITv0hVZNDF0Kv25ElAz4kkRPyqb151rgIyxzOWG"}, {"type": "function_call", "name": "execute", "arguments": "{\"command\":\"sh ./summarize.sh\",\"timeout\":120}", "call_id": "call_UhZPcsWNlrqTM86fvtiZZuIF", "id": "fc_0305eb8a54a04ee3006ab5a3a77a9887d2898254c46a853836", "index": 1}]
-{"name": "execute", "args": {"command": "sh ./summarize.sh", "timeout": 120}, "id": "call_UhZPcsWNlrqTM86fvtiZZuIF", "type": "tool_call"}</t>
+    <t>{"name": "execute", "args": {"command": "sh ./summarize.sh"}, "id": "shell-call-2", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -363,13 +452,13 @@
     <t>Tool · execute</t>
   </si>
   <si>
-    <t>01a0d587-4733-7281-936a-e7b34c0438ff</t>
+    <t>01a1143f-945b-7492-bd69-502bf356d2ed</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'command': 'sh ./summarize.sh', 'timeout': 120}</t>
+    <t>{'command': 'sh ./summarize.sh'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
@@ -383,7 +472,7 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0d587-4750-7b32-ad48-53449c4e54b6</t>
+    <t>01a1143f-947a-7761-809b-b8500c708224</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -392,7 +481,10 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "Orders: 3  \nTotal units: 9  \n\nExit status: 0", "phase": "final_answer", "index": 0, "id": "msg_0305eb8a54a04ee3006ab5a3a8587487d29bf4cf5a0efbfa68"}]</t>
+    <t>Shell tool returned:
+Orders: 3
+Total units: 9
+[Command succeeded with exit code 0]</t>
   </si>
   <si>
     <t>shell_agent</t>
@@ -407,46 +499,37 @@
     <t>Subtree total</t>
   </si>
   <si>
-    <t xml:space="preserve">    PatchToolCallsMiddleware.before_agent</t>
-  </si>
-  <si>
-    <t>Check message history and repair missing tool responses before the agent starts.</t>
-  </si>
-  <si>
-    <t>01a0d587-42f2-7a62-b6bb-a43ef2a73202</t>
+    <t xml:space="preserve">    model</t>
+  </si>
+  <si>
+    <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
+  </si>
+  <si>
+    <t>01a1143f-93d8-7e51-92df-a4ba793b45d3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ShellFixture</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>Run a local script through DeepAgent’s native execute tool.</t>
+  </si>
+  <si>
+    <t>Own call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    tools</t>
+  </si>
+  <si>
+    <t>Execute tool calls requested by the preceding model response and return their observations.</t>
+  </si>
+  <si>
+    <t>01a1143f-945b-7492-bd69-5015b7bea39e</t>
   </si>
   <si>
     <t>No model charge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    model</t>
-  </si>
-  <si>
-    <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
-  </si>
-  <si>
-    <t>01a0d587-42f3-7e71-b2d4-6e6610c51eb3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ChatOpenAI</t>
-  </si>
-  <si>
-    <t>model</t>
-  </si>
-  <si>
-    <t>Generate the next assistant message or tool request from the current conversation.</t>
-  </si>
-  <si>
-    <t>Own call</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    tools</t>
-  </si>
-  <si>
-    <t>Execute tool calls requested by the preceding model response and return their observations.</t>
-  </si>
-  <si>
-    <t>01a0d587-4732-7661-be25-1701b031358e</t>
   </si>
   <si>
     <t xml:space="preserve">        execute</t>
@@ -460,13 +543,11 @@
 - Quote paths containing spaces (e.g. cd "/path/with spaces").
 - Chain commands with ';' or '&amp;&amp;' (use '&amp;&amp;' when a command depends on the previous); do not use newlines except inside quoted strings.
 - Use absolute paths and avoid `cd` so the working directory stays stable; use the optional timeout to override the default.
-- You MUST avoid using search commands like find and grep. Instead use the grep, glob tools to search. Use read_file rather than cat/head/tail.
-    - execute(command="find . -name '*.py'")  # Use glob tool instead
-    - execute(command="grep -r 'pattern' .")  # Use grep tool instead
+- Use read_file rather than cat/head/tail.
 Only available on backends implementing SandboxBackendProtocol; otherwise it returns an error.</t>
   </si>
   <si>
-    <t>01a0d587-474e-7bb2-9895-90f97a30614a</t>
+    <t>01a1143f-9479-7923-9b51-8ebcab66ae69</t>
   </si>
 </sst>
 </file>
@@ -873,7 +954,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -930,23 +1011,23 @@
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="C2" s="4" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006239467976</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
+        <v>0.0002759040588</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00070924</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
+        <v>0.00031362</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>28.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>71.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -954,578 +1035,558 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006239467976</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
+        <v>0.0002759040588</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00070924</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
+        <v>0.00031362</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>28.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>71.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D4" s="4">
-        <v>2310</v>
+        <v>793</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D5" s="5">
-        <v>3</v>
+        <v>793</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>0.000139526764</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B22),D5*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>0.0001586</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>129</v>
+      </c>
+      <c r="D6" s="1">
+        <v>655</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="73" customHeight="1">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="1">
         <v>99</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>132</v>
+      </c>
+      <c r="D8" s="1">
+        <v>39</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2307</v>
-      </c>
-      <c r="E9" s="2">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000507390045</v>
-      </c>
-      <c r="F9" s="2">
-        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00057675</v>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
+        <v>134</v>
+      </c>
+      <c r="D9" s="1">
+        <v>793</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D10" s="1">
+        <v>793</v>
+      </c>
+      <c r="L10" s="1">
+        <v>793</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B11" s="4">
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D11" s="4">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D12" s="5">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.501192e-06</v>
+        <v>6.1229904e-05</v>
       </c>
       <c r="F12" s="2">
-        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.08e-05</v>
+        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E22),D12*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>6.96e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H12" s="5">
         <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="24" customHeight="1">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="34" customHeight="1">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="5">
-        <v>28</v>
-      </c>
-      <c r="E13" s="2">
-        <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.9559264e-05</v>
-      </c>
-      <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.36e-05</v>
-      </c>
-      <c r="G13" s="5">
-        <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H13" s="5">
-        <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="281" customHeight="1">
+        <v>138</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>109</v>
+        <v>134</v>
+      </c>
+      <c r="D14" s="1">
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="24" customHeight="1">
-      <c r="A16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D15" s="1">
+        <v>58</v>
+      </c>
+      <c r="L15" s="1">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E12)=2,SUM('Turns'!E5,'Turns'!E12),"Unknown")</f>
+        <v>0.000200756668</v>
+      </c>
+      <c r="F16" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F12)=2,SUM('Turns'!F5,'Turns'!F12),"Unknown")</f>
+        <v>0.0002282</v>
+      </c>
+      <c r="G16" s="5">
+        <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>20.0</v>
+      </c>
+      <c r="H16" s="5">
+        <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>23.0</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="B17" s="4">
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13)=4,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.000546978345</v>
-      </c>
-      <c r="F17" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13)=4,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.00062175</v>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
-      </c>
-      <c r="H17" s="5">
-        <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>142</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="24" customHeight="1">
+        <v>141</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="24" customHeight="1">
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="60" customHeight="1">
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="60" customHeight="1">
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="4">
-        <v>2377</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>119</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="4">
+        <v>899</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="24" customHeight="1">
+      <c r="A21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="5">
+        <v>851</v>
+      </c>
+      <c r="E21" s="2">
+        <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.49731748e-05</v>
+      </c>
+      <c r="F21" s="2">
+        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!C22),D21*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>1.702e-05</v>
+      </c>
+      <c r="G21" s="5">
+        <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H21" s="5">
+        <f>IF(ISNUMBER(F21),ROUND(F21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="24" customHeight="1">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D22" s="5">
-        <v>2307</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2">
         <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.05912036e-05</v>
+        <v>8.445504e-06</v>
       </c>
       <c r="F22" s="2">
-        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!C17),D22*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.614e-05</v>
+        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!B22),D22*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>9.6e-06</v>
       </c>
       <c r="G22" s="5">
         <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H22" s="5">
         <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="24" customHeight="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="60" customHeight="1">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="5">
-        <v>3</v>
-      </c>
-      <c r="E23" s="2">
-        <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="F23" s="2">
-        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!B17),D23*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G23" s="5">
-        <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H23" s="5">
-        <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="60" customHeight="1">
+        <v>151</v>
+      </c>
+      <c r="D23" s="1">
+        <v>48</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="24" customHeight="1">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>117</v>
+        <v>134</v>
+      </c>
+      <c r="D24" s="1">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="5">
-        <v>67</v>
-      </c>
-      <c r="E25" s="2">
-        <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.4735645e-05</v>
-      </c>
-      <c r="F25" s="2">
-        <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!D17),D25*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>1.675e-05</v>
-      </c>
-      <c r="G25" s="5">
-        <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H25" s="5">
-        <f>IF(ISNUMBER(F25),ROUND(F25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="24" customHeight="1">
-      <c r="A26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="4">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="24" customHeight="1">
+        <v>135</v>
+      </c>
+      <c r="D25" s="1">
+        <v>48</v>
+      </c>
+      <c r="L25" s="1">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="24" customHeight="1">
+      <c r="A27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="5">
+        <v>49</v>
+      </c>
+      <c r="E27" s="2">
+        <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.1728712e-05</v>
+      </c>
+      <c r="F27" s="2">
+        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!E22),D27*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>5.88e-05</v>
+      </c>
+      <c r="G27" s="5">
+        <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+      <c r="H27" s="5">
+        <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="73" customHeight="1">
       <c r="A28" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="5">
-        <v>20</v>
-      </c>
-      <c r="E28" s="2">
-        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.111376e-05</v>
-      </c>
-      <c r="F28" s="2">
-        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.4e-05</v>
-      </c>
-      <c r="G28" s="5">
-        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H28" s="5">
-        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="47" customHeight="1">
+        <v>138</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="24" customHeight="1">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>122</v>
+        <v>134</v>
+      </c>
+      <c r="D29" s="1">
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="24" customHeight="1">
-      <c r="A31" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B32" s="4">
-        <v>1</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="2">
-        <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28)=4,SUM('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28),"Unknown")</f>
-        <v>7.69684526e-05</v>
-      </c>
-      <c r="F32" s="2">
-        <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28)=4,SUM('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28),"Unknown")</f>
-        <v>8.749e-05</v>
-      </c>
-      <c r="G32" s="5">
-        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>135</v>
+      </c>
+      <c r="D30" s="1">
+        <v>49</v>
+      </c>
+      <c r="L30" s="1">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="4">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="2">
+        <f>IF(COUNT('Turns'!E21,'Turns'!E22,'Turns'!E27)=3,SUM('Turns'!E21,'Turns'!E22,'Turns'!E27),"Unknown")</f>
+        <v>7.51473908e-05</v>
+      </c>
+      <c r="F31" s="2">
+        <f>IF(COUNT('Turns'!F21,'Turns'!F22,'Turns'!F27)=3,SUM('Turns'!F21,'Turns'!F22,'Turns'!F27),"Unknown")</f>
+        <v>8.542e-05</v>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
         <v>8.0</v>
       </c>
-      <c r="H32" s="5">
-        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="H31" s="5">
+        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
         <v>9.0</v>
       </c>
-      <c r="K32" s="4" t="s">
-        <v>111</v>
+      <c r="K31" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE32">
+  <conditionalFormatting sqref="A2:AE31">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1539,7 +1600,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -1646,177 +1707,241 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D23)=2,SUM('Turns'!D5,'Turns'!D23),"Unknown")</f>
-        <v>6.0</v>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D22)=2,SUM('Turns'!D5,'Turns'!D22),"Unknown")</f>
+        <v>841.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E23)=2,SUM('Turns'!E5,'Turns'!E23),"Unknown")</f>
-        <v>1.055688e-06</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E22)=2,SUM('Turns'!E5,'Turns'!E22),"Unknown")</f>
+        <v>0.000147972268</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F23)=2,SUM('Turns'!F5,'Turns'!F23),"Unknown")</f>
-        <v>1.2e-06</v>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F22)=2,SUM('Turns'!F5,'Turns'!F22),"Unknown")</f>
+        <v>0.0001682</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>2307.0</v>
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>851.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>4.05912036e-05</v>
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>1.49731748e-05</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.614e-05</v>
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>1.702e-05</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D9,'Turns'!D25)=2,SUM('Turns'!D9,'Turns'!D25),"Unknown")</f>
-        <v>2374.0</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E9,'Turns'!E25)=2,SUM('Turns'!E9,'Turns'!E25),"Unknown")</f>
-        <v>0.00052212569</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F9,'Turns'!F25)=2,SUM('Turns'!F9,'Turns'!F25),"Unknown")</f>
-        <v>0.0005935</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D28)=2,SUM('Turns'!D13,'Turns'!D28),"Unknown")</f>
-        <v>48.0</v>
+        <f>IF(COUNT('Turns'!D12,'Turns'!D27)=2,SUM('Turns'!D12,'Turns'!D27),"Unknown")</f>
+        <v>107.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
-        <v>5.0673024e-05</v>
+        <f>IF(COUNT('Turns'!E12,'Turns'!E27)=2,SUM('Turns'!E12,'Turns'!E27),"Unknown")</f>
+        <v>0.000112958616</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
-        <v>5.76e-05</v>
+        <f>IF(COUNT('Turns'!F12,'Turns'!F27)=2,SUM('Turns'!F12,'Turns'!F27),"Unknown")</f>
+        <v>0.0001284</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>9.0</v>
+        <v>0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.501192e-06</v>
+        <v>0</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006239467976</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31)=2,SUM('Turns'!E16,'Turns'!E31),"Unknown")</f>
+        <v>0.0002759040588</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00070924</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31)=2,SUM('Turns'!F16,'Turns'!F31),"Unknown")</f>
+        <v>0.00031362</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>28.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>71.0</v>
+        <v>31.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2045.869</v>
+        <v>165.617</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="H3" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
+      <c r="J3" s="2">
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>793.0</v>
+      </c>
+      <c r="K3" s="2">
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>0.000139526764</v>
+      </c>
+      <c r="L3" s="2">
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
+        <v>0.0001586</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2">
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>58.0</v>
+      </c>
+      <c r="T3" s="2">
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>6.1229904e-05</v>
+      </c>
+      <c r="U3" s="2">
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>6.96e-05</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="2">
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.000200756668</v>
+      </c>
+      <c r="Z3" s="2">
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.0002282</v>
+      </c>
+      <c r="AA3" s="5">
+        <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>20.0</v>
+      </c>
+      <c r="AB3" s="5">
+        <f>IF(ISNUMBER(Z3),ROUND(Z3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>23.0</v>
+      </c>
       <c r="AD3" s="1">
-        <v>0.394</v>
+        <v>129.658</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="F4" s="1">
+        <v>793</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="H4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="J4" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
+        <v>793.0</v>
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <v>0.000139526764</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
+        <v>0.0001586</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>
@@ -1828,311 +1953,299 @@
         <v>0</v>
       </c>
       <c r="P4" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2307.0</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.000507390045</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00057675</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>28.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>58.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>2.9559264e-05</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>6.1229904e-05</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.36e-05</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>6.96e-05</v>
       </c>
       <c r="V4" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>9.0</v>
+        <v>0</v>
       </c>
       <c r="W4" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.501192e-06</v>
+        <v>0</v>
       </c>
       <c r="X4" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.08e-05</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000546978345</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.000200756668</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00062175</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.0002282</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>20.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
+        <v>23.0</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="AD4" s="1">
-        <v>1085.967</v>
+        <v>126.794</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2310</v>
+        <v>141</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="I5" t="s">
-        <v>133</v>
-      </c>
-      <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2307.0</v>
-      </c>
-      <c r="Q5" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.000507390045</v>
-      </c>
-      <c r="R5" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.00057675</v>
-      </c>
-      <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>28.0</v>
-      </c>
-      <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>2.9559264e-05</v>
-      </c>
-      <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.36e-05</v>
-      </c>
-      <c r="V5" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="W5" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.501192e-06</v>
-      </c>
-      <c r="X5" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.08e-05</v>
-      </c>
-      <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000546978345</v>
-      </c>
-      <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.00062175</v>
-      </c>
-      <c r="AA5" s="5">
-        <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
-      </c>
-      <c r="AB5" s="5">
-        <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>62.0</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="AD5" s="1">
-        <v>1079.331</v>
+        <v>29.222</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="H6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="AD6" s="1">
-        <v>27.424</v>
+        <v>27.393</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="I7" t="s">
-        <v>140</v>
+        <v>49</v>
+      </c>
+      <c r="J7" s="2">
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>48.0</v>
+      </c>
+      <c r="K7" s="2">
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>8.445504e-06</v>
+      </c>
+      <c r="L7" s="2">
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>9.6e-06</v>
+      </c>
+      <c r="M7" s="2">
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>851.0</v>
+      </c>
+      <c r="N7" s="2">
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>1.49731748e-05</v>
+      </c>
+      <c r="O7" s="2">
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>1.702e-05</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>49.0</v>
+      </c>
+      <c r="T7" s="2">
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>5.1728712e-05</v>
+      </c>
+      <c r="U7" s="2">
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>5.88e-05</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>7.51473908e-05</v>
+      </c>
+      <c r="Z7" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>8.542e-05</v>
+      </c>
+      <c r="AA7" s="5">
+        <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="AB7" s="5">
+        <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>25.297</v>
+        <v>3.17</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="F8" s="1">
+        <v>899</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="H8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="J8" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <v>48.0</v>
       </c>
       <c r="K8" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <v>8.445504e-06</v>
       </c>
       <c r="L8" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <v>9.6e-06</v>
       </c>
       <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>2307.0</v>
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>851.0</v>
       </c>
       <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>4.05912036e-05</v>
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>1.49731748e-05</v>
       </c>
       <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.614e-05</v>
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>1.702e-05</v>
       </c>
       <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>67.0</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>1.4735645e-05</v>
+        <v>0</v>
       </c>
       <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>1.675e-05</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>20.0</v>
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>49.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.111376e-05</v>
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>5.1728712e-05</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>2.4e-05</v>
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>5.88e-05</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
@@ -2144,12 +2257,12 @@
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.69684526e-05</v>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>7.51473908e-05</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>8.749e-05</v>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>8.542e-05</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2159,126 +2272,18 @@
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
         <v>9.0</v>
       </c>
+      <c r="AC8" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="AD8" s="1">
-        <v>926.0700000000001</v>
+        <v>1.835</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" ht="54" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="1">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2377</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="H9" t="s">
-        <v>119</v>
-      </c>
-      <c r="I9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J9" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K9" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L9" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M9" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
-        <v>2307.0</v>
-      </c>
-      <c r="N9" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
-        <v>4.05912036e-05</v>
-      </c>
-      <c r="O9" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
-        <v>4.614e-05</v>
-      </c>
-      <c r="P9" s="2">
-        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>67.0</v>
-      </c>
-      <c r="Q9" s="2">
-        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>1.4735645e-05</v>
-      </c>
-      <c r="R9" s="2">
-        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>1.675e-05</v>
-      </c>
-      <c r="S9" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>20.0</v>
-      </c>
-      <c r="T9" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.111376e-05</v>
-      </c>
-      <c r="U9" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>2.4e-05</v>
-      </c>
-      <c r="V9" s="2">
-        <v>0</v>
-      </c>
-      <c r="W9" s="2">
-        <v>0</v>
-      </c>
-      <c r="X9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>7.69684526e-05</v>
-      </c>
-      <c r="Z9" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>8.749e-05</v>
-      </c>
-      <c r="AA9" s="5">
-        <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="AB9" s="5">
-        <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="AC9" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>922.1950000000001</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE9">
+  <conditionalFormatting sqref="A2:AE8">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>
@@ -2292,7 +2297,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -2677,6 +2682,731 @@
         <v>80</v>
       </c>
     </row>
+    <row r="23" spans="1:9" ht="72" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E23" s="2">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="72" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E24" s="2">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="72" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="2">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D25" s="2">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2">
+        <v>20</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="72" customHeight="1">
+      <c r="A26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E26" s="2">
+        <v>15</v>
+      </c>
+      <c r="F26" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="72" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E27" s="2">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="72" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="72" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D29" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="F29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="72" customHeight="1">
+      <c r="A30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3.00</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="72" customHeight="1">
+      <c r="A31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="72" customHeight="1">
+      <c r="A32" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.075</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="72" customHeight="1">
+      <c r="A33" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.175</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="F33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="72" customHeight="1">
+      <c r="A34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="72" customHeight="1">
+      <c r="A35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="D35" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="F35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="72" customHeight="1">
+      <c r="A36" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="72" customHeight="1">
+      <c r="A37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="72" customHeight="1">
+      <c r="A38" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="72" customHeight="1">
+      <c r="A39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="2">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E39" s="2">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2">
+        <v>50</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="72" customHeight="1">
+      <c r="A40" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="72" customHeight="1">
+      <c r="A41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E41" s="2">
+        <v>10</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="72" customHeight="1">
+      <c r="A42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E42" s="2">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="72" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="F43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="72" customHeight="1">
+      <c r="A44" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="D44" s="2">
+        <v>25.00</v>
+      </c>
+      <c r="E44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="F44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="72" customHeight="1">
+      <c r="A45" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="72" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.40</v>
+      </c>
+      <c r="D46" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="72" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
